--- a/data/satisfaction_summary/2026/9月/9月客户类型满意度汇总表.xlsx
+++ b/data/satisfaction_summary/2026/9月/9月客户类型满意度汇总表.xlsx
@@ -586,20 +586,20 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>9.26</v>
+        <v>9.4</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>9.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>9.140000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>9.15</v>
+        <v>9.42</v>
       </c>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
@@ -1104,22 +1104,22 @@
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="4" t="n">
-        <v>9.69</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>9.67</v>
+        <v>9.68</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9.539999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>9.48</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>9.210000000000001</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
   </sheetData>
